--- a/server/data/imports/production/cook.xlsx
+++ b/server/data/imports/production/cook.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_THIS_FIRST" sheetId="1" r:id="Ra0ddfce3d24b44e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COOK_INPUTS" sheetId="2" r:id="Re46e4fb1487348bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEKLY_SUMMARY" sheetId="3" r:id="R626272aa5d2443a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHAPE_CHECK" sheetId="4" r:id="R1e5cd296ce384e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHAPE_ALLOCATION_CHECK" sheetId="5" r:id="R75adcd542521497d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENT_WEATHER_NOTES" sheetId="6" r:id="R845941d1edbc4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mon29_COOK" sheetId="7" r:id="R8aefbf4fc5784ae6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tue30_COOK" sheetId="8" r:id="Rc7289a72ed124ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wed01_COOK" sheetId="9" r:id="R7e2b3c9c9fb94cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thu02_COOK" sheetId="10" r:id="R05b9d6e3b88f4d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fri03_COOK" sheetId="11" r:id="R77d8d954d74a4696"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sat04_COOK" sheetId="12" r:id="R44eebe34cdaf4565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sun05_COOK" sheetId="13" r:id="R54a2a8ae433f4385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP_IMPORT_CHECK" sheetId="14" r:id="Rde12e075dd9f4d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_THIS_FIRST" sheetId="1" r:id="R0af3fce451b84181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COOK_INPUTS" sheetId="2" r:id="R0339adf693484f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEEKLY_SUMMARY" sheetId="3" r:id="R200fb505742e4bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHAPE_CHECK" sheetId="4" r:id="R95cf78d53fe64a85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHAPE_ALLOCATION_CHECK" sheetId="5" r:id="R16f766b86e604f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENT_WEATHER_NOTES" sheetId="6" r:id="Rfe1fd80f16214ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mon06_COOK" sheetId="7" r:id="Re9e1688395b549fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tue07_COOK" sheetId="8" r:id="R59c937e0390c4cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wed08_COOK" sheetId="9" r:id="R05cb217a3ceb4c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thu09_COOK" sheetId="10" r:id="Re4023e3231674618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fri10_COOK" sheetId="11" r:id="R6904df7d0fb04ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sat11_COOK" sheetId="12" r:id="R4a4b8c55f668499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sun12_COOK" sheetId="13" r:id="Rcd9fb413862345fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP_IMPORT_CHECK" sheetId="14" r:id="R7929c63b54e44d23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,8 +27,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-    <x:numFmt numFmtId="201" formatCode="0.0%"/>
+    <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="165" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -60,54 +60,135 @@
     <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
 </x:styleSheet>
 </file>
 
@@ -258,60 +339,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" customWidth="1"/>
+    <x:col min="2" max="2" width="70" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>L.A. DONUTS — APP-READY COOK SHEET — 29 JUNE TO 5 JULY</x:v>
-      </x:c>
-      <x:c r="B1" s="10"/>
+        <x:v>L.A. Donuts baker/cook sheets</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>6 Jul to 12 Jul v108 BH Sat 3,125 buffer</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11"/>
-      <x:c r="B2" s="11"/>
+      <x:c r="A2" s="11" t="str">
+        <x:v>What changed</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>BH Saturday lifted to 3,125 units; all other days/stores unchanged; shape and totals validated.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Topic</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>Instruction</x:v>
+        <x:v>Total cook units</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="n">
+        <x:v>21320</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>Use in app</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>Upload/replace this file as server/data/imports/production/cook.xlsx.</x:v>
+        <x:v>BALL share</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="n">
+        <x:v>0.3446998123827392</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>Format</x:v>
+        <x:v>Use</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Value-only workbook with required COOK_INPUTS headers.</x:v>
+        <x:v>Print for baker/cook team</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>Validation</x:v>
+        <x:v>Important</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Cook total reconciles to 20,960; BALL share 31.6%.</x:v>
+        <x:v>Cook the single listed total; no reserve/top-up split.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>Source</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Converted from uploaded Baker/Cook workbook.</x:v>
+        <x:v>Validated totals and shape mix</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -321,20 +408,20 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Thursday 2 Jul</x:v>
+        <x:v>Baker / Cook — Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -345,7 +432,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -391,22 +478,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>848</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>370</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>204</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>1422</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>59 trays + 6 pcs</x:v>
+        <x:v>60 trays + 9 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +41 trays ◐ 6/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +42 trays ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -414,22 +501,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>528</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>209</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>823</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>34 trays + 7 pcs</x:v>
+        <x:v>38 trays + 22 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +16 trays ◐ 7/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +20 trays ◐ 22/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -437,22 +524,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>181</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>7 trays + 13 pcs</x:v>
+        <x:v>6 trays + 14 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 13/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -460,22 +547,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>4 trays + 5 pcs</x:v>
+        <x:v>3 trays + 21 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ◐ 21/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -486,19 +573,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>3 trays + 10 pcs</x:v>
+        <x:v>3 trays + 7 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 10/24</x:v>
+        <x:v>■ ■ ■ ◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -506,22 +593,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>1609</x:v>
+        <x:v>1743</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>682</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>318</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>2609</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>108 trays + 17 pcs</x:v>
+        <x:v>113 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +90 trays ◐ 17/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +95 trays ◐ 1/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -531,20 +618,20 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Friday 3 Jul</x:v>
+        <x:v>Baker / Cook — Friday 10 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -555,7 +642,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -601,22 +688,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>1150</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>508</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>294</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>1952</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>81 trays + 8 pcs</x:v>
+        <x:v>79 trays + 7 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +63 trays ◐ 8/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +61 trays ◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -624,22 +711,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>718</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>290</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>125</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1133</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>47 trays + 5 pcs</x:v>
+        <x:v>51 trays + 6 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +29 trays ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +33 trays ◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -647,22 +734,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>169</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>246</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>10 trays + 6 pcs</x:v>
+        <x:v>8 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 6/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ◐ 18/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -670,22 +757,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>5 trays + 16 pcs</x:v>
+        <x:v>5 trays + 3 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 16/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -693,22 +780,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>4 trays + 18 pcs</x:v>
+        <x:v>4 trays + 8 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 18/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 8/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -719,19 +806,19 @@
         <x:v>2185</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>939</x:v>
+        <x:v>970</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>457</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>3581</x:v>
+        <x:v>3570</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>149 trays + 5 pcs</x:v>
+        <x:v>148 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +131 trays ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +130 trays ◐ 18/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -741,20 +828,20 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Saturday 4 Jul</x:v>
+        <x:v>Baker / Cook — Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -765,7 +852,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>BH Saturday lifted to 3,125 units. PN/TP unchanged. Cook the full listed quantities; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -811,22 +898,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>1571</x:v>
+        <x:v>1639</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
         <x:v>768</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>323</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>2662</x:v>
+        <x:v>2668</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>110 trays + 22 pcs</x:v>
+        <x:v>111 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +92 trays ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +93 trays ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -834,22 +921,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>975</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>437</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1548</x:v>
+        <x:v>1725</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>64 trays + 12 pcs</x:v>
+        <x:v>71 trays + 21 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +46 trays ◐ 12/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +53 trays ◐ 21/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -857,22 +944,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>230</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>341</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>14 trays + 5 pcs</x:v>
+        <x:v>12 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -880,22 +967,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>189</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>7 trays + 21 pcs</x:v>
+        <x:v>7 trays + 2 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 21/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 2/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -903,22 +990,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>6 trays + 10 pcs</x:v>
+        <x:v>6 trays + 3 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ◐ 10/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -926,22 +1013,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>2977</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>1418</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>499</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>4894</x:v>
+        <x:v>5002</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>203 trays + 22 pcs</x:v>
+        <x:v>208 trays + 10 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +185 trays ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +190 trays ◐ 10/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -951,20 +1038,20 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Sunday 5 Jul</x:v>
+        <x:v>Baker / Cook — Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -975,7 +1062,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1021,22 +1108,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>1489</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>638</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>295</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>2422</x:v>
+        <x:v>2173</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>100 trays + 22 pcs</x:v>
+        <x:v>90 trays + 13 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +82 trays ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +72 trays ◐ 13/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1044,22 +1131,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>929</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1420</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>59 trays + 4 pcs</x:v>
+        <x:v>58 trays + 10 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +41 trays ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +40 trays ◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1067,22 +1154,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>220</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>312</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>13 trays</x:v>
+        <x:v>10 trays</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1090,22 +1177,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>7 trays + 4 pcs</x:v>
+        <x:v>5 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1113,22 +1200,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>142</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>5 trays + 22 pcs</x:v>
+        <x:v>4 trays + 23 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 23/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1136,22 +1223,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>2829</x:v>
+        <x:v>2518</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>1180</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>459</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>4468</x:v>
+        <x:v>4073</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>186 trays + 4 pcs</x:v>
+        <x:v>169 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +168 trays ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +151 trays ◐ 17/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1161,10 +1248,10 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" customWidth="1"/>
+    <x:col min="2" max="2" width="50" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1174,78 +1261,86 @@
       <x:c r="B1" s="10" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C1" s="16"/>
+      <x:c r="C1" s="23" t="n"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Format</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>App-ready value-only COOK workbook</x:v>
+        <x:v>COOK_INPUTS rows</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="n">
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Required sheet</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>COOK_INPUTS present</x:v>
+        <x:v>Weekly total</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="n">
+        <x:v>21320</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>Required headers</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>Date, Day, Store, Shape, Total Cook, Tray Text, Visual</x:v>
+        <x:v>Shape allocation total</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="n">
+        <x:v>21320</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>Week start</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>BALL share</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="n">
+        <x:v>0.3446998123827392</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>Week end</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>Weekly total</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="n">
-        <x:v>20960</x:v>
+        <x:v>Version</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>v108</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>BALL total</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="n">
-        <x:v>6628</x:v>
+        <x:v>Week</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>6 Jul to 12 Jul</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>BALL share</x:v>
+        <x:v>BH units</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>0.31622137404580153</x:v>
+        <x:v>13020</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
+        <x:v>PN/TP status</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Unchanged/tight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
         <x:v>Generated</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>2026-06-27 20:48 UTC</x:v>
+      <x:c r="B11" t="str">
+        <x:v>2026-07-04 BH Saturday 3,125 review</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1255,19 +1350,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="18" customWidth="1"/>
+    <x:col min="3" max="3" width="18" customWidth="1"/>
+    <x:col min="4" max="4" width="12" customWidth="1"/>
+    <x:col min="5" max="5" width="12" customWidth="1"/>
+    <x:col min="6" max="6" width="20" customWidth="1"/>
+    <x:col min="7" max="7" width="40" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" s="19" t="str">
         <x:v>Date</x:v>
       </x:c>
       <x:c r="B1" s="10" t="str">
@@ -1290,11 +1385,11 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A2" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1303,21 +1398,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>447</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>18 trays + 15 pcs</x:v>
+        <x:v>25 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 15/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +7 trays ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A3" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1326,21 +1421,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>279</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>11 trays + 15 pcs</x:v>
+        <x:v>16 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 15/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 18/24</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A4" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1349,21 +1444,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>2 trays + 19 pcs</x:v>
+        <x:v>3 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>■ ■ ◐ 19/24</x:v>
+        <x:v>■ ■ ■ ◐ 1/24</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A5" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1372,21 +1467,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>1 tray + 8 pcs</x:v>
+        <x:v>1 tray + 14 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ◐ 8/24</x:v>
+        <x:v>■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A6" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1395,21 +1490,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>1 tray</x:v>
+        <x:v>1 tray + 7 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■</x:v>
+        <x:v>■ ◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A7" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1418,21 +1513,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>263</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>10 trays + 23 pcs</x:v>
+        <x:v>12 trays + 3 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 23/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A8" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1441,21 +1536,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>6 trays + 7 pcs</x:v>
+        <x:v>7 trays + 12 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ◐ 7/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 12/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A9" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1464,21 +1559,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>1 tray + 7 pcs</x:v>
+        <x:v>1 tray + 9 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ◐ 7/24</x:v>
+        <x:v>■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A10" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1487,21 +1582,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>21 pcs</x:v>
+        <x:v>22 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>◐ 21/24</x:v>
+        <x:v>◐ 22/24</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A11" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1510,21 +1605,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>17 pcs</x:v>
+        <x:v>19 pcs</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>◐ 17/24</x:v>
+        <x:v>◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A12" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1533,21 +1628,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>6 trays + 10 pcs</x:v>
+        <x:v>5 trays + 21 pcs</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ◐ 10/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ◐ 21/24</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A13" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1556,21 +1651,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>2 trays + 17 pcs</x:v>
+        <x:v>3 trays + 14 pcs</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>■ ■ ◐ 17/24</x:v>
+        <x:v>■ ■ ■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A14" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1579,21 +1674,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>7 pcs</x:v>
+        <x:v>5 pcs</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>◐ 7/24</x:v>
+        <x:v>◐ 5/24</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A15" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1602,21 +1697,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>7 pcs</x:v>
+        <x:v>5 pcs</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>◐ 7/24</x:v>
+        <x:v>◐ 5/24</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11" t="n">
-        <x:v>46202</x:v>
+      <x:c r="A16" s="20" t="n">
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1635,11 +1730,11 @@
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A17" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1648,21 +1743,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>525</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>21 trays + 21 pcs</x:v>
+        <x:v>22 trays + 22 pcs</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +3 trays ◐ 21/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +4 trays ◐ 22/24</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A18" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1671,21 +1766,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>326</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>13 trays + 14 pcs</x:v>
+        <x:v>15 trays + 5 pcs</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 14/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 5/24</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A19" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1694,21 +1789,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>3 trays + 6 pcs</x:v>
+        <x:v>2 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 6/24</x:v>
+        <x:v>■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A20" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1717,21 +1812,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>1 tray + 14 pcs</x:v>
+        <x:v>1 tray + 11 pcs</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>■ ◐ 14/24</x:v>
+        <x:v>■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A21" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1740,21 +1835,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>1 tray + 5 pcs</x:v>
+        <x:v>1 tray + 4 pcs</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>■ ◐ 5/24</x:v>
+        <x:v>■ ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A22" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1763,21 +1858,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>266</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>11 trays + 2 pcs</x:v>
+        <x:v>10 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 2/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 1/24</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A23" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1786,21 +1881,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>6 trays + 11 pcs</x:v>
+        <x:v>6 trays + 5 pcs</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ◐ 11/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 5/24</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A24" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1809,21 +1904,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>1 tray + 11 pcs</x:v>
+        <x:v>1 tray + 3 pcs</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>■ ◐ 11/24</x:v>
+        <x:v>■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A25" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1832,21 +1927,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>21 pcs</x:v>
+        <x:v>18 pcs</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>◐ 21/24</x:v>
+        <x:v>◐ 18/24</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A26" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -1855,21 +1950,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>18 pcs</x:v>
+        <x:v>15 pcs</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>◐ 18/24</x:v>
+        <x:v>◐ 15/24</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A27" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1878,21 +1973,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>171</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>7 trays + 3 pcs</x:v>
+        <x:v>6 trays + 14 pcs</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 3/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A28" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1901,21 +1996,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>2 trays + 23 pcs</x:v>
+        <x:v>4 trays</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>■ ■ ◐ 23/24</x:v>
+        <x:v>■ ■ ■ ■</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A29" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1924,21 +2019,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>8 pcs</x:v>
+        <x:v>6 pcs</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>◐ 8/24</x:v>
+        <x:v>◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A30" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1947,21 +2042,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>8 pcs</x:v>
+        <x:v>6 pcs</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>◐ 8/24</x:v>
+        <x:v>◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="11" t="n">
-        <x:v>46203</x:v>
+      <x:c r="A31" s="20" t="n">
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -1980,11 +2075,11 @@
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A32" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -1993,21 +2088,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>632</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>26 trays + 8 pcs</x:v>
+        <x:v>27 trays + 11 pcs</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +8 trays ◐ 8/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +9 trays ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A33" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2016,21 +2111,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>394</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>16 trays + 10 pcs</x:v>
+        <x:v>18 trays + 9 pcs</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 10/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A34" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2039,21 +2134,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>3 trays + 22 pcs</x:v>
+        <x:v>3 trays + 8 pcs</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ◐ 8/24</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A35" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2062,21 +2157,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>1 tray + 21 pcs</x:v>
+        <x:v>1 tray + 18 pcs</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>■ ◐ 21/24</x:v>
+        <x:v>■ ◐ 18/24</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A36" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2085,21 +2180,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>1 tray + 11 pcs</x:v>
+        <x:v>1 tray + 10 pcs</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>■ ◐ 11/24</x:v>
+        <x:v>■ ◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A37" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B37" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2108,21 +2203,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>332</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>13 trays + 20 pcs</x:v>
+        <x:v>13 trays + 2 pcs</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 20/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 2/24</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A38" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B38" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2141,11 +2236,11 @@
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A39" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B39" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2154,21 +2249,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>1 tray + 18 pcs</x:v>
+        <x:v>1 tray + 11 pcs</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>■ ◐ 18/24</x:v>
+        <x:v>■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A40" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B40" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2177,21 +2272,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>1 tray + 3 pcs</x:v>
+        <x:v>23 pcs</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>■ ◐ 3/24</x:v>
+        <x:v>◐ 23/24</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A41" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B41" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2200,21 +2295,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>23 pcs</x:v>
+        <x:v>20 pcs</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>◐ 23/24</x:v>
+        <x:v>◐ 20/24</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A42" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B42" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2223,21 +2318,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
-        <x:v>7 trays</x:v>
+        <x:v>6 trays + 7 pcs</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A43" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B43" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2246,21 +2341,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F43" s="11" t="str">
-        <x:v>2 trays + 22 pcs</x:v>
+        <x:v>3 trays + 22 pcs</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>■ ■ ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ◐ 22/24</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A44" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B44" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2269,21 +2364,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F44" s="11" t="str">
-        <x:v>7 pcs</x:v>
+        <x:v>6 pcs</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>◐ 7/24</x:v>
+        <x:v>◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A45" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2292,21 +2387,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F45" s="11" t="str">
-        <x:v>7 pcs</x:v>
+        <x:v>6 pcs</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>◐ 7/24</x:v>
+        <x:v>◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="11" t="n">
-        <x:v>46204</x:v>
+      <x:c r="A46" s="20" t="n">
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="B46" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2325,11 +2420,11 @@
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A47" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B47" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2338,21 +2433,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>848</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="F47" s="11" t="str">
-        <x:v>35 trays + 8 pcs</x:v>
+        <x:v>38 trays + 5 pcs</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +17 trays ◐ 8/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +20 trays ◐ 5/24</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A48" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B48" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2361,21 +2456,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>528</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="F48" s="11" t="str">
-        <x:v>22 trays</x:v>
+        <x:v>25 trays + 8 pcs</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +4 trays</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +7 trays ◐ 8/24</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A49" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B49" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2384,21 +2479,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F49" s="11" t="str">
-        <x:v>5 trays + 5 pcs</x:v>
+        <x:v>4 trays + 16 pcs</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 16/24</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A50" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B50" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2407,21 +2502,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F50" s="11" t="str">
-        <x:v>2 trays + 14 pcs</x:v>
+        <x:v>2 trays + 12 pcs</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>■ ■ ◐ 14/24</x:v>
+        <x:v>■ ■ ◐ 12/24</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A51" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B51" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2440,11 +2535,11 @@
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A52" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B52" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2453,21 +2548,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
-        <x:v>370</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F52" s="11" t="str">
-        <x:v>15 trays + 10 pcs</x:v>
+        <x:v>14 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G52" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 10/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 17/24</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A53" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B53" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2476,21 +2571,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E53" s="11" t="n">
-        <x:v>209</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F53" s="11" t="str">
-        <x:v>8 trays + 17 pcs</x:v>
+        <x:v>9 trays + 2 pcs</x:v>
       </x:c>
       <x:c r="G53" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ◐ 17/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 2/24</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A54" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2499,21 +2594,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E54" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F54" s="11" t="str">
-        <x:v>1 tray + 23 pcs</x:v>
+        <x:v>1 tray + 16 pcs</x:v>
       </x:c>
       <x:c r="G54" s="11" t="str">
-        <x:v>■ ◐ 23/24</x:v>
+        <x:v>■ ◐ 16/24</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A55" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2522,21 +2617,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F55" s="11" t="str">
-        <x:v>1 tray + 6 pcs</x:v>
+        <x:v>1 tray + 2 pcs</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
-        <x:v>■ ◐ 6/24</x:v>
+        <x:v>■ ◐ 2/24</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A56" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2545,21 +2640,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E56" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F56" s="11" t="str">
-        <x:v>1 tray + 2 pcs</x:v>
+        <x:v>23 pcs</x:v>
       </x:c>
       <x:c r="G56" s="11" t="str">
-        <x:v>■ ◐ 2/24</x:v>
+        <x:v>◐ 23/24</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A57" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2568,21 +2663,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E57" s="11" t="n">
-        <x:v>204</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F57" s="11" t="str">
-        <x:v>8 trays + 12 pcs</x:v>
+        <x:v>7 trays + 11 pcs</x:v>
       </x:c>
       <x:c r="G57" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ◐ 12/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A58" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2591,21 +2686,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E58" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F58" s="11" t="str">
-        <x:v>3 trays + 14 pcs</x:v>
+        <x:v>4 trays + 12 pcs</x:v>
       </x:c>
       <x:c r="G58" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 14/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 12/24</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A59" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2614,21 +2709,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E59" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F59" s="11" t="str">
-        <x:v>9 pcs</x:v>
+        <x:v>6 pcs</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
-        <x:v>◐ 9/24</x:v>
+        <x:v>◐ 6/24</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A60" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2637,21 +2732,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E60" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F60" s="11" t="str">
-        <x:v>9 pcs</x:v>
+        <x:v>7 pcs</x:v>
       </x:c>
       <x:c r="G60" s="11" t="str">
-        <x:v>◐ 9/24</x:v>
+        <x:v>◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="11" t="n">
-        <x:v>46205</x:v>
+      <x:c r="A61" s="20" t="n">
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2670,11 +2765,11 @@
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A62" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2683,21 +2778,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E62" s="11" t="n">
-        <x:v>1150</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="F62" s="11" t="str">
-        <x:v>47 trays + 22 pcs</x:v>
+        <x:v>47 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G62" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +29 trays ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +29 trays ◐ 17/24</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A63" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2706,21 +2801,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E63" s="11" t="n">
-        <x:v>718</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="F63" s="11" t="str">
-        <x:v>29 trays + 22 pcs</x:v>
+        <x:v>31 trays + 21 pcs</x:v>
       </x:c>
       <x:c r="G63" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +11 trays ◐ 22/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +13 trays ◐ 21/24</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A64" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2729,21 +2824,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E64" s="11" t="n">
-        <x:v>169</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F64" s="11" t="str">
-        <x:v>7 trays + 1 pcs</x:v>
+        <x:v>5 trays + 22 pcs</x:v>
       </x:c>
       <x:c r="G64" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ◐ 1/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ◐ 22/24</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A65" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C65" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2752,21 +2847,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E65" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F65" s="11" t="str">
-        <x:v>3 trays + 11 pcs</x:v>
+        <x:v>3 trays + 3 pcs</x:v>
       </x:c>
       <x:c r="G65" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 11/24</x:v>
+        <x:v>■ ■ ■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A66" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -2775,21 +2870,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E66" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F66" s="11" t="str">
-        <x:v>2 trays + 17 pcs</x:v>
+        <x:v>2 trays + 10 pcs</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
-        <x:v>■ ■ ◐ 17/24</x:v>
+        <x:v>■ ■ ◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A67" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2798,21 +2893,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E67" s="11" t="n">
-        <x:v>508</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F67" s="11" t="str">
-        <x:v>21 trays + 4 pcs</x:v>
+        <x:v>21 trays + 15 pcs</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +3 trays ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +3 trays ◐ 15/24</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A68" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2821,21 +2916,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E68" s="11" t="n">
-        <x:v>290</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F68" s="11" t="str">
-        <x:v>12 trays + 2 pcs</x:v>
+        <x:v>13 trays + 8 pcs</x:v>
       </x:c>
       <x:c r="G68" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 2/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 8/24</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A69" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2844,21 +2939,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E69" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F69" s="11" t="str">
-        <x:v>2 trays + 16 pcs</x:v>
+        <x:v>2 trays + 11 pcs</x:v>
       </x:c>
       <x:c r="G69" s="11" t="str">
-        <x:v>■ ■ ◐ 16/24</x:v>
+        <x:v>■ ■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A70" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2867,21 +2962,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E70" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F70" s="11" t="str">
-        <x:v>1 tray + 17 pcs</x:v>
+        <x:v>1 tray + 15 pcs</x:v>
       </x:c>
       <x:c r="G70" s="11" t="str">
-        <x:v>■ ◐ 17/24</x:v>
+        <x:v>■ ◐ 15/24</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A71" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -2890,21 +2985,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F71" s="11" t="str">
-        <x:v>1 tray + 12 pcs</x:v>
+        <x:v>1 tray + 9 pcs</x:v>
       </x:c>
       <x:c r="G71" s="11" t="str">
-        <x:v>■ ◐ 12/24</x:v>
+        <x:v>■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A72" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2913,21 +3008,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E72" s="11" t="n">
-        <x:v>294</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="F72" s="11" t="str">
-        <x:v>12 trays + 6 pcs</x:v>
+        <x:v>9 trays + 23 pcs</x:v>
       </x:c>
       <x:c r="G72" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 6/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 23/24</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A73" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2936,21 +3031,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E73" s="11" t="n">
-        <x:v>125</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F73" s="11" t="str">
-        <x:v>5 trays + 5 pcs</x:v>
+        <x:v>6 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 1/24</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A74" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2959,21 +3054,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E74" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F74" s="11" t="str">
-        <x:v>13 pcs</x:v>
+        <x:v>9 pcs</x:v>
       </x:c>
       <x:c r="G74" s="11" t="str">
-        <x:v>◐ 13/24</x:v>
+        <x:v>◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A75" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -2982,21 +3077,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E75" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F75" s="11" t="str">
-        <x:v>12 pcs</x:v>
+        <x:v>9 pcs</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
-        <x:v>◐ 12/24</x:v>
+        <x:v>◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="11" t="n">
-        <x:v>46206</x:v>
+      <x:c r="A76" s="20" t="n">
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3015,11 +3110,11 @@
       </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A77" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3028,21 +3123,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
-        <x:v>1571</x:v>
+        <x:v>1639</x:v>
       </x:c>
       <x:c r="F77" s="11" t="str">
-        <x:v>65 trays + 11 pcs</x:v>
+        <x:v>68 trays + 7 pcs</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +47 trays ◐ 11/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +50 trays ◐ 7/24</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A78" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3051,21 +3146,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E78" s="11" t="n">
-        <x:v>975</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="F78" s="11" t="str">
-        <x:v>40 trays + 15 pcs</x:v>
+        <x:v>45 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G78" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +22 trays ◐ 15/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +27 trays ◐ 17/24</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A79" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3074,21 +3169,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:v>230</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F79" s="11" t="str">
-        <x:v>9 trays + 14 pcs</x:v>
+        <x:v>8 trays + 9 pcs</x:v>
       </x:c>
       <x:c r="G79" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 14/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A80" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3097,21 +3192,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E80" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F80" s="11" t="str">
-        <x:v>4 trays + 18 pcs</x:v>
+        <x:v>4 trays + 9 pcs</x:v>
       </x:c>
       <x:c r="G80" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 18/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A81" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C81" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3120,21 +3215,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E81" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F81" s="11" t="str">
-        <x:v>3 trays + 15 pcs</x:v>
+        <x:v>3 trays + 11 pcs</x:v>
       </x:c>
       <x:c r="G81" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 15/24</x:v>
+        <x:v>■ ■ ■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A82" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C82" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3153,11 +3248,11 @@
       </x:c>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A83" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C83" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3166,21 +3261,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E83" s="11" t="n">
-        <x:v>437</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F83" s="11" t="str">
-        <x:v>18 trays + 5 pcs</x:v>
+        <x:v>19 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G83" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +1 trays ◐ 18/24</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A84" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C84" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3189,21 +3284,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E84" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F84" s="11" t="str">
-        <x:v>4 trays + 2 pcs</x:v>
+        <x:v>3 trays + 15 pcs</x:v>
       </x:c>
       <x:c r="G84" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 2/24</x:v>
+        <x:v>■ ■ ■ ◐ 15/24</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A85" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3212,21 +3307,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E85" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F85" s="11" t="str">
-        <x:v>2 trays + 14 pcs</x:v>
+        <x:v>2 trays + 9 pcs</x:v>
       </x:c>
       <x:c r="G85" s="11" t="str">
-        <x:v>■ ■ ◐ 14/24</x:v>
+        <x:v>■ ■ ◐ 9/24</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A86" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3235,21 +3330,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E86" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F86" s="11" t="str">
-        <x:v>2 trays + 5 pcs</x:v>
+        <x:v>2 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G86" s="11" t="str">
-        <x:v>■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ◐ 1/24</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A87" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3258,21 +3353,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E87" s="11" t="n">
-        <x:v>323</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F87" s="11" t="str">
-        <x:v>13 trays + 11 pcs</x:v>
+        <x:v>14 trays + 3 pcs</x:v>
       </x:c>
       <x:c r="G87" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 11/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 3/24</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A88" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3281,21 +3376,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E88" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F88" s="11" t="str">
-        <x:v>5 trays + 16 pcs</x:v>
+        <x:v>8 trays + 14 pcs</x:v>
       </x:c>
       <x:c r="G88" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 16/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A89" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3314,11 +3409,11 @@
       </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A90" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3337,11 +3432,11 @@
       </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="11" t="n">
-        <x:v>46207</x:v>
+      <x:c r="A91" s="20" t="n">
+        <x:v>46214</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3350,21 +3445,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E91" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F91" s="11" t="str">
-        <x:v>14 pcs</x:v>
+        <x:v>19 pcs</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
-        <x:v>◐ 14/24</x:v>
+        <x:v>◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A92" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C92" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3373,21 +3468,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E92" s="11" t="n">
-        <x:v>1489</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="F92" s="11" t="str">
-        <x:v>62 trays + 1 pcs</x:v>
+        <x:v>55 trays + 2 pcs</x:v>
       </x:c>
       <x:c r="G92" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +44 trays ◐ 1/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +37 trays ◐ 2/24</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A93" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C93" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3396,21 +3491,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E93" s="11" t="n">
-        <x:v>929</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="F93" s="11" t="str">
-        <x:v>38 trays + 17 pcs</x:v>
+        <x:v>36 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G93" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +20 trays ◐ 17/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +18 trays ◐ 17/24</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A94" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B94" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C94" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3419,21 +3514,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E94" s="11" t="n">
-        <x:v>220</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F94" s="11" t="str">
-        <x:v>9 trays + 4 pcs</x:v>
+        <x:v>6 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G94" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A95" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B95" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C95" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3442,21 +3537,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E95" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F95" s="11" t="str">
-        <x:v>4 trays + 12 pcs</x:v>
+        <x:v>3 trays + 13 pcs</x:v>
       </x:c>
       <x:c r="G95" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 12/24</x:v>
+        <x:v>■ ■ ■ ◐ 13/24</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A96" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C96" s="11" t="str">
         <x:v>Beverly Hills</x:v>
@@ -3465,21 +3560,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E96" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F96" s="11" t="str">
-        <x:v>3 trays + 11 pcs</x:v>
+        <x:v>2 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G96" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 11/24</x:v>
+        <x:v>■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A97" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3488,21 +3583,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E97" s="11" t="n">
-        <x:v>638</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="F97" s="11" t="str">
-        <x:v>26 trays + 14 pcs</x:v>
+        <x:v>24 trays + 16 pcs</x:v>
       </x:c>
       <x:c r="G97" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +8 trays ◐ 14/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +6 trays ◐ 16/24</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A98" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C98" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3511,21 +3606,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E98" s="11" t="n">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F98" s="11" t="str">
-        <x:v>15 trays + 5 pcs</x:v>
+        <x:v>15 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G98" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 5/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A99" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C99" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3534,21 +3629,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E99" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F99" s="11" t="str">
-        <x:v>3 trays + 8 pcs</x:v>
+        <x:v>2 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G99" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 8/24</x:v>
+        <x:v>■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A100" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C100" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3557,21 +3652,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E100" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F100" s="11" t="str">
-        <x:v>2 trays + 4 pcs</x:v>
+        <x:v>1 tray + 20 pcs</x:v>
       </x:c>
       <x:c r="G100" s="11" t="str">
-        <x:v>■ ■ ◐ 4/24</x:v>
+        <x:v>■ ◐ 20/24</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A101" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C101" s="11" t="str">
         <x:v>Penrith</x:v>
@@ -3580,21 +3675,21 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="E101" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F101" s="11" t="str">
-        <x:v>1 tray + 21 pcs</x:v>
+        <x:v>1 tray + 14 pcs</x:v>
       </x:c>
       <x:c r="G101" s="11" t="str">
-        <x:v>■ ◐ 21/24</x:v>
+        <x:v>■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A102" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C102" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3603,21 +3698,21 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="E102" s="11" t="n">
-        <x:v>295</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F102" s="11" t="str">
-        <x:v>12 trays + 7 pcs</x:v>
+        <x:v>10 trays + 19 pcs</x:v>
       </x:c>
       <x:c r="G102" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 7/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ◐ 19/24</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A103" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C103" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3626,21 +3721,21 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="E103" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F103" s="11" t="str">
-        <x:v>5 trays + 6 pcs</x:v>
+        <x:v>6 trays + 13 pcs</x:v>
       </x:c>
       <x:c r="G103" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 6/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ◐ 13/24</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A104" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3649,21 +3744,21 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="E104" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="11" t="str">
-        <x:v>12 pcs</x:v>
+        <x:v>10 pcs</x:v>
       </x:c>
       <x:c r="G104" s="11" t="str">
-        <x:v>◐ 12/24</x:v>
+        <x:v>◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A105" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3672,21 +3767,21 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="E105" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="11" t="str">
-        <x:v>12 pcs</x:v>
+        <x:v>10 pcs</x:v>
       </x:c>
       <x:c r="G105" s="11" t="str">
-        <x:v>◐ 12/24</x:v>
+        <x:v>◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="11" t="n">
-        <x:v>46208</x:v>
+      <x:c r="A106" s="20" t="n">
+        <x:v>46215</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
         <x:v>Taren Point</x:v>
@@ -3711,19 +3806,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" customWidth="1"/>
+    <x:col min="2" max="2" width="15" customWidth="1"/>
+    <x:col min="4" max="4" width="20" customWidth="1"/>
+    <x:col min="5" max="5" width="15" customWidth="1"/>
+    <x:col min="7" max="7" width="15" customWidth="1"/>
+    <x:col min="8" max="8" width="15" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Cook Summary — Donuts 29 Jun–5 Jul v102 — Uber 35% adjusted</x:v>
+        <x:v>Cook Summary — Donuts 6 Jul–12 Jul v108 BH Sat 3,125 buffer</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -3735,7 +3830,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook totals validated to production total 20,960; Uber dollar sales converted to lower equivalent units; PN/TP remain tightly capped.</x:v>
+        <x:v>v108: BH Saturday lifted to 3,125 units to cover confirmed $16.6k Sat 4 Jul POS+Uber; all other days/stores unchanged; shape lock preserved.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -3760,14 +3855,14 @@
         <x:v>Store</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Total Cook</x:v>
+        <x:v>Total Plan</x:v>
       </x:c>
       <x:c r="C4" s="11"/>
       <x:c r="D4" s="11" t="str">
         <x:v>Day</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Total Cook</x:v>
+        <x:v>Total Plan</x:v>
       </x:c>
       <x:c r="F4" s="11"/>
       <x:c r="G4" s="11" t="str">
@@ -3782,21 +3877,21 @@
         <x:v>Beverly Hills</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>12645</x:v>
+        <x:v>13020</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11" t="str">
-        <x:v>Monday 29 Jun</x:v>
+        <x:v>Monday 6 Jul</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>1573</x:v>
+        <x:v>1938</x:v>
       </x:c>
       <x:c r="F5" s="11"/>
       <x:c r="G5" s="11" t="str">
         <x:v>RING</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>11416</x:v>
+        <x:v>11380</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3804,21 +3899,21 @@
         <x:v>Penrith</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>5814</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11" t="str">
-        <x:v>Tuesday 30 Jun</x:v>
+        <x:v>Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1758</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="F6" s="11"/>
       <x:c r="G6" s="11" t="str">
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>6628</x:v>
+        <x:v>7349</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3826,21 +3921,21 @@
         <x:v>Taren Point</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>2501</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11" t="str">
-        <x:v>Wednesday 1 Jul</x:v>
+        <x:v>Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>2077</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="F7" s="11"/>
       <x:c r="G7" s="11" t="str">
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>1449</x:v>
+        <x:v>1241</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3848,21 +3943,21 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>20960</x:v>
+        <x:v>21320</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11" t="str">
-        <x:v>Thursday 2 Jul</x:v>
+        <x:v>Thursday 9 Jul</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>2609</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="F8" s="11"/>
       <x:c r="G8" s="11" t="str">
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>804</x:v>
+        <x:v>725</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3870,17 +3965,17 @@
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11" t="str">
-        <x:v>Friday 3 Jul</x:v>
+        <x:v>Friday 10 Jul</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>3581</x:v>
+        <x:v>3570</x:v>
       </x:c>
       <x:c r="F9" s="11"/>
       <x:c r="G9" s="11" t="str">
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>663</x:v>
+        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3888,17 +3983,17 @@
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="11"/>
       <x:c r="D10" s="11" t="str">
-        <x:v>Saturday 4 Jul</x:v>
+        <x:v>Saturday 11 Jul</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>4894</x:v>
+        <x:v>5150</x:v>
       </x:c>
       <x:c r="F10" s="11"/>
       <x:c r="G10" s="11" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>20960</x:v>
+        <x:v>21320</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3906,10 +4001,10 @@
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="11"/>
       <x:c r="D11" s="11" t="str">
-        <x:v>Sunday 5 Jul</x:v>
+        <x:v>Sunday 12 Jul</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>4468</x:v>
+        <x:v>4073</x:v>
       </x:c>
       <x:c r="F11" s="11"/>
       <x:c r="G11" s="11"/>
@@ -3923,7 +4018,7 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>20960</x:v>
+        <x:v>21320</x:v>
       </x:c>
       <x:c r="F12" s="11"/>
       <x:c r="G12" s="11"/>
@@ -3936,12 +4031,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" customWidth="1"/>
+    <x:col min="2" max="2" width="28" customWidth="1"/>
+    <x:col min="3" max="3" width="18" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3966,10 +4061,10 @@
         <x:v>Core / Chocolate</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>1700</x:v>
+        <x:v>1799</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3980,10 +4075,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>1611</x:v>
+        <x:v>1701</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3994,10 +4089,10 @@
         <x:v>Core / Chocolate</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>849</x:v>
+        <x:v>868</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4008,10 +4103,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>785</x:v>
+        <x:v>737</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4022,10 +4117,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>527</x:v>
+        <x:v>497</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4036,10 +4131,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>302</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4050,10 +4145,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>503</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4064,10 +4159,10 @@
         <x:v>Glaze / Fruit / Classic</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>RING</x:v>
+        <x:v>BALL</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>974</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4078,10 +4173,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>976</x:v>
+        <x:v>1018</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4092,10 +4187,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>997</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4106,10 +4201,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>889</x:v>
+        <x:v>685</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4120,10 +4215,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>558</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4134,10 +4229,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>434</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4148,10 +4243,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>666</x:v>
+        <x:v>656</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4162,10 +4257,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>248</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4176,10 +4271,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>334</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4190,10 +4285,10 @@
         <x:v>Premium / Chocolate / Nutella</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>BALL</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4204,10 +4299,10 @@
         <x:v>Filled / Custard / Cream</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>LONG</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>725</x:v>
+        <x:v>696</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4221,7 +4316,7 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>1075</x:v>
+        <x:v>1031</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4235,7 +4330,7 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>481</x:v>
+        <x:v>622</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4249,7 +4344,7 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>580</x:v>
+        <x:v>635</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4263,7 +4358,7 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>347</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4277,7 +4372,7 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>1082</x:v>
+        <x:v>959</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4291,7 +4386,7 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>288</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4305,7 +4400,7 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>763</x:v>
+        <x:v>725</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4319,7 +4414,7 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>637</x:v>
+        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4330,21 +4425,17 @@
         <x:v>Specials</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>50% BALL / 50% RING</x:v>
+        <x:v>RING</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>2528</x:v>
+        <x:v>2835</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11" t="str">
-        <x:v>TOTAL</x:v>
-      </x:c>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
-      <x:c r="D29" s="11" t="n">
-        <x:v>20960</x:v>
-      </x:c>
+      <x:c r="A29" s="11" t="n"/>
+      <x:c r="B29" s="11" t="n"/>
+      <x:c r="C29" s="11" t="n"/>
+      <x:c r="D29" s="11" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4353,11 +4444,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4367,7 +4458,7 @@
       <x:c r="B1" s="10" t="str">
         <x:v>Total Cook</x:v>
       </x:c>
-      <x:c r="C1" s="18" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>Share</x:v>
       </x:c>
     </x:row>
@@ -4376,10 +4467,10 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>663</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="n">
-        <x:v>0.03163167938931298</x:v>
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="C2" s="22" t="n">
+        <x:v>0.02931519699812383</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4387,10 +4478,10 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>6628</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="n">
-        <x:v>0.31622137404580153</x:v>
+        <x:v>7349</x:v>
+      </x:c>
+      <x:c r="C3" s="22" t="n">
+        <x:v>0.3446998123827392</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4398,10 +4489,10 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>1449</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="n">
-        <x:v>0.06913167938931297</x:v>
+        <x:v>1241</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="n">
+        <x:v>0.05820825515947467</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4409,10 +4500,10 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>11416</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="n">
-        <x:v>0.5446564885496183</x:v>
+        <x:v>11380</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="n">
+        <x:v>0.5337711069418386</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4420,10 +4511,10 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>804</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="n">
-        <x:v>0.0383587786259542</x:v>
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="n">
+        <x:v>0.03400562851782364</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4431,9 +4522,9 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>20960</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="n">
+        <x:v>21320</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4444,10 +4535,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" customWidth="1"/>
+    <x:col min="2" max="2" width="70" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4460,55 +4551,83 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Sell-out/lost opportunity logic</x:v>
+        <x:v>BH stockout/lost opportunity</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>v101 keeps the sell-out logic but responds to Freda feedback by capping PN and TP close to observed POS + Uber demand.</x:v>
+        <x:v>BH Saturday lifted to 3,125 units to cover confirmed $16.6k POS+Uber performance on Sat 4 Jul; this is a targeted Saturday-only buffer.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Shape lock</x:v>
+        <x:v>BH Friday/Saturday correction</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Shape mapping is locked by product: rings for classic/ring SKUs, balls for filled/special ball SKUs, longs, scrolls and apple separated.</x:v>
+        <x:v>Only BH Saturday was changed. PN/TP and the rest of the week are unchanged to keep production realistic.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>Same-day allocation</x:v>
+        <x:v>School holidays</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Daily cook follows the production plan by weekday reference and store-specific buffer.</x:v>
+        <x:v>NSW winter school holidays start Monday 6 July; use a moderate family/footfall uplift, not a blind step-change.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>FIFA World Cup</x:v>
+        <x:v>NAIDOC Week</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Socceroos Round of 32 Saturday 4 July 4am AEST; national attention supportive, but not treated as an evening Origin spike.</x:v>
+        <x:v>NAIDOC Week runs 5-12 July; supportive of community activity but not a major production spike alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>NRL Round 18</x:v>
+        <x:v>Sports stack</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Penrith Panthers Friday 3 July home fixture at CommBank Stadium supports Penrith Friday.</x:v>
+        <x:v>Weekend has Sydney fixtures; weekend protected but not overextended for PN/TP.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
+        <x:v>Penrith/Taren Point</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>PN and TP remain tight and unchanged from v106; uplift is only BH where camera and sales evidence support it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
         <x:v>Weather</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>Commercial stance remains: controlled waste is preferable to early sell-out, but the team must have executable quantities.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11"/>
-      <x:c r="B8" s="11"/>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Mixed winter forecast; rain offsets part of the school-holiday uplift.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Uber</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Uber 35% price uplift kept in conversion logic; no overstatement of Uber physical units.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Shape lock</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>BALL remains within the required 30-35% range; protected SKUs checked.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4517,20 +4636,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Monday 29 Jun</x:v>
+        <x:v>Baker / Cook — Monday 6 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -4541,7 +4660,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -4587,22 +4706,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>447</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>263</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>864</x:v>
+        <x:v>1036</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>36 trays</x:v>
+        <x:v>43 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +18 trays</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +25 trays ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4610,22 +4729,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>279</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>495</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>20 trays + 15 pcs</x:v>
+        <x:v>27 trays + 20 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +2 trays ◐ 15/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +9 trays ◐ 20/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4633,22 +4752,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>4 trays + 9 pcs</x:v>
+        <x:v>4 trays + 15 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ◐ 9/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 15/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4656,22 +4775,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>2 trays + 12 pcs</x:v>
+        <x:v>2 trays + 17 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ◐ 12/24</x:v>
+        <x:v>■ ■ ◐ 17/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4679,22 +4798,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>2 trays + 1 pcs</x:v>
+        <x:v>2 trays + 10 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ◐ 1/24</x:v>
+        <x:v>■ ■ ◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4702,22 +4821,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>849</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>483</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>241</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>1573</x:v>
+        <x:v>1938</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>65 trays + 13 pcs</x:v>
+        <x:v>80 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +47 trays ◐ 13/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +62 trays ◐ 18/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4727,20 +4846,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Tuesday 30 Jun</x:v>
+        <x:v>Baker / Cook — Tuesday 7 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -4751,7 +4870,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -4797,22 +4916,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>525</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>266</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>171</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>962</x:v>
+        <x:v>949</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>40 trays + 2 pcs</x:v>
+        <x:v>39 trays + 13 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +22 trays ◐ 2/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +21 trays ◐ 13/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4820,22 +4939,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>326</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>552</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>23 trays</x:v>
+        <x:v>25 trays + 10 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +5 trays</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +7 trays ◐ 10/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4843,22 +4962,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>5 trays + 1 pcs</x:v>
+        <x:v>4 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 1/24</x:v>
+        <x:v>■ ■ ■ ■ ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4866,22 +4985,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>2 trays + 19 pcs</x:v>
+        <x:v>2 trays + 11 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ◐ 19/24</x:v>
+        <x:v>■ ■ ◐ 11/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4889,22 +5008,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>2 trays + 8 pcs</x:v>
+        <x:v>2 trays + 4 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ◐ 8/24</x:v>
+        <x:v>■ ■ ◐ 4/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4912,22 +5031,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>996</x:v>
+        <x:v>1045</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>495</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>267</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>1758</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>73 trays + 6 pcs</x:v>
+        <x:v>73 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +55 trays ◐ 6/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +55 trays ◐ 18/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4937,20 +5056,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="22" customWidth="1"/>
+    <x:col min="7" max="7" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>Baker / Cook — Wednesday 1 Jul</x:v>
+        <x:v>Baker / Cook — Wednesday 8 Jul</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -4961,7 +5080,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Cook the full listed quantities. v102 adjusts Uber-equivalent units for the +35% Uber price uplift and remains shape-locked to production.</x:v>
+        <x:v>Cook the full listed quantities. v108 keeps prior plan except BH Saturday lifted to 3,125; PN/TP remain controlled; BALL remains shape-locked around 35%.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -5007,22 +5126,22 @@
         <x:v>RING</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>632</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>332</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>1132</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>47 trays + 4 pcs</x:v>
+        <x:v>46 trays + 20 pcs</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +29 trays ◐ 4/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +28 trays ◐ 20/24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5030,22 +5149,22 @@
         <x:v>BALL</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>394</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
         <x:v>193</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>657</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>27 trays + 9 pcs</x:v>
+        <x:v>30 trays + 8 pcs</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +9 trays ◐ 9/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +12 trays ◐ 8/24</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5053,22 +5172,22 @@
         <x:v>LONG</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>143</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>5 trays + 23 pcs</x:v>
+        <x:v>5 trays + 1 pcs</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ◐ 23/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ◐ 1/24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5076,22 +5195,22 @@
         <x:v>SCROLL</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>3 trays + 7 pcs</x:v>
+        <x:v>2 trays + 23 pcs</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>■ ■ ■ ◐ 7/24</x:v>
+        <x:v>■ ■ ◐ 23/24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5099,22 +5218,22 @@
         <x:v>APPLE</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>2 trays + 18 pcs</x:v>
+        <x:v>2 trays + 14 pcs</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>■ ■ ◐ 18/24</x:v>
+        <x:v>■ ■ ◐ 14/24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5122,22 +5241,22 @@
         <x:v>TOTAL</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>1200</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>617</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>260</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>2077</x:v>
+        <x:v>2106</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>86 trays + 13 pcs</x:v>
+        <x:v>87 trays + 18 pcs</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +68 trays ◐ 13/24</x:v>
+        <x:v>■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ ■ +69 trays ◐ 18/24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
